--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.35884048890614</v>
+        <v>6.558311579447248</v>
       </c>
       <c r="D2" t="n">
-        <v>44.96973938352448</v>
+        <v>7.307582649822728</v>
       </c>
       <c r="E2" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F2" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.53012502540428</v>
+        <v>5.936145316628196</v>
       </c>
       <c r="D3" t="n">
-        <v>42.36332600522008</v>
+        <v>6.884040475848264</v>
       </c>
       <c r="E3" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F3" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.67675208887856</v>
+        <v>3.847472214442766</v>
       </c>
       <c r="D4" t="n">
-        <v>21.413875228679</v>
+        <v>3.479754724660338</v>
       </c>
       <c r="E4" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F4" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.73963975479914</v>
+        <v>5.807691460154861</v>
       </c>
       <c r="D5" t="n">
-        <v>35.03266440376391</v>
+        <v>5.692807965611635</v>
       </c>
       <c r="E5" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F5" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.80890460099956</v>
+        <v>4.193946997662429</v>
       </c>
       <c r="D6" t="n">
-        <v>25.62438592617978</v>
+        <v>4.163962713004214</v>
       </c>
       <c r="E6" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F6" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.58614541529335</v>
+        <v>8.545248629985171</v>
       </c>
       <c r="D7" t="n">
-        <v>53.32547363372102</v>
+        <v>8.665389465479667</v>
       </c>
       <c r="E7" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F7" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.807976231637371</v>
+        <v>1.268796137641073</v>
       </c>
       <c r="D8" t="n">
-        <v>10.12990298278424</v>
+        <v>1.646109234702439</v>
       </c>
       <c r="E8" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F8" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.4891395264308</v>
+        <v>6.904485173045006</v>
       </c>
       <c r="D9" t="n">
-        <v>43.6995803582036</v>
+        <v>7.101181808208086</v>
       </c>
       <c r="E9" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F9" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.52941117315079</v>
+        <v>2.686029315637003</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64448400060214</v>
+        <v>3.029728650097848</v>
       </c>
       <c r="E10" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F10" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.1097678043762</v>
+        <v>5.542837268211132</v>
       </c>
       <c r="D11" t="n">
-        <v>35.69627189431021</v>
+        <v>5.80064418282541</v>
       </c>
       <c r="E11" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F11" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.0937109487466</v>
+        <v>7.815228029171323</v>
       </c>
       <c r="D12" t="n">
-        <v>50.50840273450461</v>
+        <v>8.207615444357</v>
       </c>
       <c r="E12" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F12" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>59.72875106789969</v>
+        <v>9.705922048533701</v>
       </c>
       <c r="D13" t="n">
-        <v>62.10750105577928</v>
+        <v>10.09246892156413</v>
       </c>
       <c r="E13" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F13" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>74.63090670840091</v>
+        <v>12.12752234011515</v>
       </c>
       <c r="D14" t="n">
-        <v>76.81685109488909</v>
+        <v>12.48273830291948</v>
       </c>
       <c r="E14" t="n">
-        <v>17.32440843180291</v>
+        <v>2.815216370167973</v>
       </c>
       <c r="F14" t="n">
-        <v>17.80181167745347</v>
+        <v>2.892794397586189</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
